--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_deer_buck_conservation.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_deer_buck_conservation.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +47,13 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -65,8 +70,23 @@
         <fgColor rgb="004F2D1D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B301B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F1E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFE5D7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -88,11 +108,25 @@
         <color rgb="00D8B58E"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C58F61"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C58F61"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C58F61"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C58F61"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -114,6 +148,39 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,315 +574,315 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>hunt_name</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>hunt_code</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>sex_type</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>hunt_type</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>permits_2026_res</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>permits_2026_nr</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>permits_2026_total</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Harvest Prior Year</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Percent Harvest Success (previous hunting season)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Average Age Harvested (previous hunting season)</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Book Cliffs (North &amp; South)</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>DB1056</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Buck</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>Deer</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>Oct 17, 2026 - Oct 25, 2026</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr"/>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="6" t="inlineStr"/>
-      <c r="K2" s="6" t="inlineStr"/>
-      <c r="L2" s="7" t="n">
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
+      <c r="J2" s="16" t="inlineStr"/>
+      <c r="K2" s="15" t="inlineStr"/>
+      <c r="L2" s="15" t="n">
         <v>2025</v>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr"/>
+      <c r="O2" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Book Cliffs (North &amp; South)</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>DB1075</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Buck</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Deer</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>Aug 16 2025 - Sept 12 2025</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr"/>
-      <c r="K3" s="6" t="inlineStr"/>
-      <c r="L3" s="7" t="n">
+      <c r="H3" s="18" t="inlineStr"/>
+      <c r="I3" s="17" t="inlineStr"/>
+      <c r="J3" s="18" t="inlineStr"/>
+      <c r="K3" s="17" t="inlineStr"/>
+      <c r="L3" s="17" t="n">
         <v>2024</v>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="N3" s="18" t="inlineStr"/>
+      <c r="O3" s="18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Book Cliffs (North &amp; South)</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>DB1076</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Buck</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Deer</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Sept 24 2025 - Oct 02 2025</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr"/>
-      <c r="K4" s="6" t="inlineStr"/>
-      <c r="L4" s="7" t="n">
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
+      <c r="J4" s="16" t="inlineStr"/>
+      <c r="K4" s="15" t="inlineStr"/>
+      <c r="L4" s="15" t="n">
         <v>2024</v>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="N4" s="16" t="inlineStr"/>
+      <c r="O4" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>DB1118</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Buck</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Deer</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Arch: Oct 31-Nov 13, 2026 | Any Legal Weapon: Nov 14-22, 2026 | Muzz: Nov 23-Dec 1, 2026</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr"/>
-      <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="7" t="n"/>
-      <c r="M5" s="7" t="n"/>
-      <c r="N5" s="7" t="n"/>
-      <c r="O5" s="7" t="n"/>
+      <c r="H5" s="18" t="inlineStr"/>
+      <c r="I5" s="17" t="inlineStr"/>
+      <c r="J5" s="18" t="inlineStr"/>
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="17" t="n"/>
+      <c r="M5" s="18" t="n"/>
+      <c r="N5" s="18" t="n"/>
+      <c r="O5" s="18" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O5"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
-  <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
